--- a/BookData1.xlsx
+++ b/BookData1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{813064C9-4AC0-4E68-83EF-FBBA4BBD3EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22440" yWindow="-14280" windowWidth="17280" windowHeight="8880" xr2:uid="{45074215-9B61-4A1C-BDA8-63B439C1A243}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45074215-9B61-4A1C-BDA8-63B439C1A243}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
